--- a/partial/sliding_window_results_window_2.xlsx
+++ b/partial/sliding_window_results_window_2.xlsx
@@ -463,13 +463,13 @@
         <v>29.15</v>
       </c>
       <c r="C2" t="n">
-        <v>28.45769926551294</v>
+        <v>29.66705863408808</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.6923007344870626</v>
+        <v>0.5170586340880767</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4792803069713264</v>
+        <v>0.2673496310850276</v>
       </c>
     </row>
     <row r="3">
@@ -480,13 +480,13 @@
         <v>29.35</v>
       </c>
       <c r="C3" t="n">
-        <v>29.07298104513369</v>
+        <v>30.15988454009383</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.2770189548663069</v>
+        <v>0.8098845400938259</v>
       </c>
       <c r="E3" t="n">
-        <v>0.07673950135522098</v>
+        <v>0.655912968282988</v>
       </c>
     </row>
     <row r="4">
@@ -497,13 +497,13 @@
         <v>29.37</v>
       </c>
       <c r="C4" t="n">
-        <v>28.98648354733675</v>
+        <v>29.84494678620212</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.3835164526632475</v>
+        <v>0.4749467862021177</v>
       </c>
       <c r="E4" t="n">
-        <v>0.147084869463401</v>
+        <v>0.2255744497237201</v>
       </c>
     </row>
     <row r="5">
@@ -514,13 +514,13 @@
         <v>29.54</v>
       </c>
       <c r="C5" t="n">
-        <v>28.90920431921203</v>
+        <v>29.24820229833501</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.6307956807879727</v>
+        <v>-0.2917977016649935</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3979031909007619</v>
+        <v>0.08514589869697256</v>
       </c>
     </row>
     <row r="6">
@@ -531,13 +531,13 @@
         <v>29.55</v>
       </c>
       <c r="C6" t="n">
-        <v>30.13803044742587</v>
+        <v>29.77028807683576</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5880304474258686</v>
+        <v>0.2202880768357574</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3457798070998673</v>
+        <v>0.04852683679599654</v>
       </c>
     </row>
     <row r="7">
@@ -548,13 +548,13 @@
         <v>29.75</v>
       </c>
       <c r="C7" t="n">
-        <v>29.81685577167374</v>
+        <v>29.56727933301249</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0668557716737368</v>
+        <v>-0.1827206669875103</v>
       </c>
       <c r="E7" t="n">
-        <v>0.004469694206090827</v>
+        <v>0.03338684214436065</v>
       </c>
     </row>
     <row r="8">
@@ -565,13 +565,13 @@
         <v>29.84</v>
       </c>
       <c r="C8" t="n">
-        <v>30.75050629839859</v>
+        <v>30.08935803597058</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9105062983985874</v>
+        <v>0.2493580359705767</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8290217194234976</v>
+        <v>0.06217943010310343</v>
       </c>
     </row>
     <row r="9">
@@ -582,13 +582,13 @@
         <v>29.81</v>
       </c>
       <c r="C9" t="n">
-        <v>30.61713050576026</v>
+        <v>29.98617848557869</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8071305057602594</v>
+        <v>0.1761784855786885</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6514596533288121</v>
+        <v>0.03103885878080017</v>
       </c>
     </row>
     <row r="10">
@@ -599,13 +599,13 @@
         <v>29.92</v>
       </c>
       <c r="C10" t="n">
-        <v>30.42709721190894</v>
+        <v>29.73711101533921</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5070972119089348</v>
+        <v>-0.1828889846607886</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2571475823258151</v>
+        <v>0.03344838071025417</v>
       </c>
     </row>
     <row r="11">
@@ -616,13 +616,13 @@
         <v>29.98</v>
       </c>
       <c r="C11" t="n">
-        <v>29.69666364499381</v>
+        <v>29.69799928907306</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.2833363550061918</v>
+        <v>-0.2820007109269405</v>
       </c>
       <c r="E11" t="n">
-        <v>0.08027949006819475</v>
+        <v>0.07952440096329984</v>
       </c>
     </row>
     <row r="12">
@@ -633,13 +633,13 @@
         <v>30.04</v>
       </c>
       <c r="C12" t="n">
-        <v>29.97555144361638</v>
+        <v>29.72613621387445</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.06444855638362412</v>
+        <v>-0.3138637861255518</v>
       </c>
       <c r="E12" t="n">
-        <v>0.004153616419933177</v>
+        <v>0.0985104762410661</v>
       </c>
     </row>
     <row r="13">
@@ -650,13 +650,13 @@
         <v>30.21</v>
       </c>
       <c r="C13" t="n">
-        <v>29.44071962030593</v>
+        <v>29.84922737223416</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.7692803796940737</v>
+        <v>-0.3607726277658401</v>
       </c>
       <c r="E13" t="n">
-        <v>0.5917923025822582</v>
+        <v>0.1301568889450694</v>
       </c>
     </row>
     <row r="14">
@@ -667,13 +667,13 @@
         <v>30.22</v>
       </c>
       <c r="C14" t="n">
-        <v>29.86526551103273</v>
+        <v>29.87118448474057</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.3547344889672672</v>
+        <v>-0.3488155152594246</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1258365576628682</v>
+        <v>0.1216722636856978</v>
       </c>
     </row>
     <row r="15">
@@ -684,13 +684,13 @@
         <v>30.38</v>
       </c>
       <c r="C15" t="n">
-        <v>29.62894127289632</v>
+        <v>29.98279341359101</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.7510587271036755</v>
+        <v>-0.3972065864089913</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5640892115585933</v>
+        <v>0.1577730722866835</v>
       </c>
     </row>
     <row r="16">
@@ -701,13 +701,13 @@
         <v>30.44</v>
       </c>
       <c r="C16" t="n">
-        <v>30.36104736073625</v>
+        <v>30.26108524161952</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.07895263926375407</v>
+        <v>-0.1789147583804827</v>
       </c>
       <c r="E16" t="n">
-        <v>0.00623351924671248</v>
+        <v>0.03201049076634649</v>
       </c>
     </row>
     <row r="17">
@@ -718,13 +718,13 @@
         <v>30.48</v>
       </c>
       <c r="C17" t="n">
-        <v>30.39606725906519</v>
+        <v>30.15278547970684</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0839327409348094</v>
+        <v>-0.3272145202931647</v>
       </c>
       <c r="E17" t="n">
-        <v>0.00704470500082983</v>
+        <v>0.1070693422906859</v>
       </c>
     </row>
     <row r="18">
@@ -735,13 +735,13 @@
         <v>30.69</v>
       </c>
       <c r="C18" t="n">
-        <v>30.69627960163829</v>
+        <v>30.19514282129561</v>
       </c>
       <c r="D18" t="n">
-        <v>0.006279601638286891</v>
+        <v>-0.4948571787043896</v>
       </c>
       <c r="E18" t="n">
-        <v>3.943339673557541e-05</v>
+        <v>0.2448836273152682</v>
       </c>
     </row>
     <row r="19">
@@ -752,13 +752,13 @@
         <v>30.75</v>
       </c>
       <c r="C19" t="n">
-        <v>30.25991957428342</v>
+        <v>30.60131952062666</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4900804257165845</v>
+        <v>-0.1486804793733363</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2401788236705487</v>
+        <v>0.02210588494668508</v>
       </c>
     </row>
     <row r="20">
@@ -769,13 +769,13 @@
         <v>30.94</v>
       </c>
       <c r="C20" t="n">
-        <v>30.71466799285631</v>
+        <v>30.67738320357709</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2253320071436882</v>
+        <v>-0.2626167964229076</v>
       </c>
       <c r="E20" t="n">
-        <v>0.05077451344340314</v>
+        <v>0.06896758176343089</v>
       </c>
     </row>
     <row r="21">
@@ -786,13 +786,13 @@
         <v>30.95</v>
       </c>
       <c r="C21" t="n">
-        <v>31.03730775975343</v>
+        <v>30.85919113487759</v>
       </c>
       <c r="D21" t="n">
-        <v>0.08730775975342908</v>
+        <v>-0.09080886512240482</v>
       </c>
       <c r="E21" t="n">
-        <v>0.007622644913162491</v>
+        <v>0.008246249984819112</v>
       </c>
     </row>
     <row r="22">
@@ -803,13 +803,13 @@
         <v>31.02</v>
       </c>
       <c r="C22" t="n">
-        <v>31.70770545872092</v>
+        <v>31.09757034944756</v>
       </c>
       <c r="D22" t="n">
-        <v>0.6877054587209166</v>
+        <v>0.07757034944756214</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4729387979545463</v>
+        <v>0.006017159113416904</v>
       </c>
     </row>
     <row r="23">
@@ -820,13 +820,13 @@
         <v>31.12</v>
       </c>
       <c r="C23" t="n">
-        <v>32.13337620006495</v>
+        <v>31.27601048597176</v>
       </c>
       <c r="D23" t="n">
-        <v>1.01337620006495</v>
+        <v>0.156010485971759</v>
       </c>
       <c r="E23" t="n">
-        <v>1.026931322858079</v>
+        <v>0.02433927173314442</v>
       </c>
     </row>
     <row r="24">
@@ -837,13 +837,13 @@
         <v>31.28</v>
       </c>
       <c r="C24" t="n">
-        <v>32.29976812191642</v>
+        <v>31.18419340973565</v>
       </c>
       <c r="D24" t="n">
-        <v>1.019768121916421</v>
+        <v>-0.09580659026435612</v>
       </c>
       <c r="E24" t="n">
-        <v>1.039927022476944</v>
+        <v>0.009178902738082216</v>
       </c>
     </row>
     <row r="25">
@@ -854,13 +854,13 @@
         <v>31.38</v>
       </c>
       <c r="C25" t="n">
-        <v>32.13093560450127</v>
+        <v>31.20860949197808</v>
       </c>
       <c r="D25" t="n">
-        <v>0.7509356045012758</v>
+        <v>-0.1713905080219149</v>
       </c>
       <c r="E25" t="n">
-        <v>0.5639042821076966</v>
+        <v>0.02937470624001008</v>
       </c>
     </row>
     <row r="26">
@@ -871,13 +871,13 @@
         <v>31.58</v>
       </c>
       <c r="C26" t="n">
-        <v>32.54529895307395</v>
+        <v>31.41963735202371</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9652989530739546</v>
+        <v>-0.1603626479762887</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9318020688056728</v>
+        <v>0.0257161788659671</v>
       </c>
     </row>
     <row r="27">
@@ -888,13 +888,13 @@
         <v>31.65</v>
       </c>
       <c r="C27" t="n">
-        <v>32.33996152515173</v>
+        <v>31.95921673663635</v>
       </c>
       <c r="D27" t="n">
-        <v>0.6899615251517304</v>
+        <v>0.3092167366363476</v>
       </c>
       <c r="E27" t="n">
-        <v>0.4760469061897019</v>
+        <v>0.09561499021603237</v>
       </c>
     </row>
     <row r="28">
@@ -905,13 +905,13 @@
         <v>31.88</v>
       </c>
       <c r="C28" t="n">
-        <v>32.99971959255687</v>
+        <v>32.68495774151191</v>
       </c>
       <c r="D28" t="n">
-        <v>1.119719592556873</v>
+        <v>0.8049577415119096</v>
       </c>
       <c r="E28" t="n">
-        <v>1.253771965955729</v>
+        <v>0.6479569656199542</v>
       </c>
     </row>
     <row r="29">
@@ -922,13 +922,13 @@
         <v>32.28</v>
       </c>
       <c r="C29" t="n">
-        <v>32.71683441576418</v>
+        <v>32.92749544001664</v>
       </c>
       <c r="D29" t="n">
-        <v>0.4368344157641815</v>
+        <v>0.6474954400166339</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1908243067960338</v>
+        <v>0.4192503448423344</v>
       </c>
     </row>
     <row r="30">
@@ -939,13 +939,13 @@
         <v>32.45</v>
       </c>
       <c r="C30" t="n">
-        <v>32.81211361359365</v>
+        <v>33.06663339335906</v>
       </c>
       <c r="D30" t="n">
-        <v>0.3621136135936425</v>
+        <v>0.6166333933590522</v>
       </c>
       <c r="E30" t="n">
-        <v>0.1311262691498458</v>
+        <v>0.3802367418054996</v>
       </c>
     </row>
     <row r="31">
@@ -956,13 +956,13 @@
         <v>32.85</v>
       </c>
       <c r="C31" t="n">
-        <v>33.00473111840309</v>
+        <v>33.23640948043696</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1547311184030917</v>
+        <v>0.38640948043696</v>
       </c>
       <c r="E31" t="n">
-        <v>0.02394171900227159</v>
+        <v>0.1493122865715614</v>
       </c>
     </row>
     <row r="32">
@@ -973,13 +973,13 @@
         <v>32.9</v>
       </c>
       <c r="C32" t="n">
-        <v>33.10571218941026</v>
+        <v>33.29977708230282</v>
       </c>
       <c r="D32" t="n">
-        <v>0.2057121894102636</v>
+        <v>0.3997770823028262</v>
       </c>
       <c r="E32" t="n">
-        <v>0.04231750487196417</v>
+        <v>0.1598217155345606</v>
       </c>
     </row>
     <row r="33">
@@ -990,13 +990,13 @@
         <v>33.1</v>
       </c>
       <c r="C33" t="n">
-        <v>33.0779625320107</v>
+        <v>33.33975343964335</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.02203746798929984</v>
+        <v>0.2397534396433443</v>
       </c>
       <c r="E33" t="n">
-        <v>0.0004856499953794152</v>
+        <v>0.05748171182081473</v>
       </c>
     </row>
     <row r="34">
@@ -1007,13 +1007,13 @@
         <v>33.4</v>
       </c>
       <c r="C34" t="n">
-        <v>34.06090076721547</v>
+        <v>33.71583827279082</v>
       </c>
       <c r="D34" t="n">
-        <v>0.6609007672154732</v>
+        <v>0.3158382727908204</v>
       </c>
       <c r="E34" t="n">
-        <v>0.4367898241060011</v>
+        <v>0.0997538145594887</v>
       </c>
     </row>
     <row r="35">
@@ -1024,13 +1024,13 @@
         <v>33.7</v>
       </c>
       <c r="C35" t="n">
-        <v>33.89679463998552</v>
+        <v>33.74213643898327</v>
       </c>
       <c r="D35" t="n">
-        <v>0.1967946399855123</v>
+        <v>0.04213643898326325</v>
       </c>
       <c r="E35" t="n">
-        <v>0.03872813032702738</v>
+        <v>0.001775479490190267</v>
       </c>
     </row>
     <row r="36">
@@ -1041,13 +1041,13 @@
         <v>34.1</v>
       </c>
       <c r="C36" t="n">
-        <v>33.98758366440517</v>
+        <v>33.83770196888512</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.1124163355948298</v>
+        <v>-0.2622980311148808</v>
       </c>
       <c r="E36" t="n">
-        <v>0.01263743250856939</v>
+        <v>0.06880025712674298</v>
       </c>
     </row>
     <row r="37">
@@ -1058,13 +1058,13 @@
         <v>34.4</v>
       </c>
       <c r="C37" t="n">
-        <v>34.27937838195894</v>
+        <v>34.26175461750775</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.1206216180410564</v>
+        <v>-0.1382453824922436</v>
       </c>
       <c r="E37" t="n">
-        <v>0.01454957473884251</v>
+        <v>0.01911178578042674</v>
       </c>
     </row>
     <row r="38">
@@ -1075,13 +1075,13 @@
         <v>34.9</v>
       </c>
       <c r="C38" t="n">
-        <v>34.74813211395009</v>
+        <v>34.53506441515873</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.1518678860499065</v>
+        <v>-0.3649355848412696</v>
       </c>
       <c r="E38" t="n">
-        <v>0.0230638548132674</v>
+        <v>0.1331779810834395</v>
       </c>
     </row>
     <row r="39">
@@ -1092,13 +1092,13 @@
         <v>35.3</v>
       </c>
       <c r="C39" t="n">
-        <v>35.88951697187024</v>
+        <v>35.41163110728882</v>
       </c>
       <c r="D39" t="n">
-        <v>0.5895169718702462</v>
+        <v>0.1116311072888223</v>
       </c>
       <c r="E39" t="n">
-        <v>0.3475302601230646</v>
+        <v>0.01246150411452856</v>
       </c>
     </row>
     <row r="40">
@@ -1109,13 +1109,13 @@
         <v>35.7</v>
       </c>
       <c r="C40" t="n">
-        <v>36.26926468172613</v>
+        <v>35.68715858908152</v>
       </c>
       <c r="D40" t="n">
-        <v>0.5692646817261249</v>
+        <v>-0.01284141091848312</v>
       </c>
       <c r="E40" t="n">
-        <v>0.3240622778607463</v>
+        <v>0.0001649018343773375</v>
       </c>
     </row>
     <row r="41">
@@ -1126,13 +1126,13 @@
         <v>36.3</v>
       </c>
       <c r="C41" t="n">
-        <v>36.20843056628006</v>
+        <v>36.03467250596535</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.09156943371993265</v>
+        <v>-0.2653274940346506</v>
       </c>
       <c r="E41" t="n">
-        <v>0.008384961191789138</v>
+        <v>0.07039867909070756</v>
       </c>
     </row>
     <row r="42">
@@ -1143,13 +1143,13 @@
         <v>36.8</v>
       </c>
       <c r="C42" t="n">
-        <v>36.69659092684201</v>
+        <v>36.6380964444557</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.1034090731579838</v>
+        <v>-0.1619035555442991</v>
       </c>
       <c r="E42" t="n">
-        <v>0.01069343641139324</v>
+        <v>0.02621276129788596</v>
       </c>
     </row>
     <row r="43">
@@ -1160,13 +1160,13 @@
         <v>37.3</v>
       </c>
       <c r="C43" t="n">
-        <v>36.68193200156335</v>
+        <v>36.75375374323595</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.6180679984366506</v>
+        <v>-0.54624625676405</v>
       </c>
       <c r="E43" t="n">
-        <v>0.3820080506914875</v>
+        <v>0.2983849730287365</v>
       </c>
     </row>
     <row r="44">
@@ -1177,13 +1177,13 @@
         <v>37.9</v>
       </c>
       <c r="C44" t="n">
-        <v>37.74507957354775</v>
+        <v>37.77578137501172</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.1549204264522501</v>
+        <v>-0.1242186249882806</v>
       </c>
       <c r="E44" t="n">
-        <v>0.02400033853214704</v>
+        <v>0.0154302667939791</v>
       </c>
     </row>
     <row r="45">
@@ -1194,13 +1194,13 @@
         <v>38.5</v>
       </c>
       <c r="C45" t="n">
-        <v>38.44558104190894</v>
+        <v>38.49756896558319</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.05441895809105546</v>
+        <v>-0.002431034416808586</v>
       </c>
       <c r="E45" t="n">
-        <v>0.00296142299971605</v>
+        <v>5.909928335707863e-06</v>
       </c>
     </row>
     <row r="46">
@@ -1211,13 +1211,13 @@
         <v>38.9</v>
       </c>
       <c r="C46" t="n">
-        <v>38.8650531928586</v>
+        <v>39.1968811618345</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.0349468071414023</v>
+        <v>0.2968811618344986</v>
       </c>
       <c r="E46" t="n">
-        <v>0.001221279329378367</v>
+        <v>0.08813842425220177</v>
       </c>
     </row>
     <row r="47">
@@ -1228,13 +1228,13 @@
         <v>39.4</v>
       </c>
       <c r="C47" t="n">
-        <v>39.23220670737122</v>
+        <v>39.67226180578425</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.1677932926287795</v>
+        <v>0.2722618057842467</v>
       </c>
       <c r="E47" t="n">
-        <v>0.02815458905120723</v>
+        <v>0.07412649088889889</v>
       </c>
     </row>
     <row r="48">
@@ -1245,13 +1245,13 @@
         <v>39.9</v>
       </c>
       <c r="C48" t="n">
-        <v>39.65413175787145</v>
+        <v>39.84535288553736</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.2458682421285445</v>
+        <v>-0.05464711446263948</v>
       </c>
       <c r="E48" t="n">
-        <v>0.0604511924873806</v>
+        <v>0.002986307119092821</v>
       </c>
     </row>
     <row r="49">
@@ -1262,13 +1262,13 @@
         <v>40.1</v>
       </c>
       <c r="C49" t="n">
-        <v>39.70824032249832</v>
+        <v>40.27265069933905</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.3917596775016818</v>
+        <v>0.1726506993390515</v>
       </c>
       <c r="E49" t="n">
-        <v>0.1534756449162218</v>
+        <v>0.02980826398226357</v>
       </c>
     </row>
     <row r="50">
@@ -1279,13 +1279,13 @@
         <v>40.6</v>
       </c>
       <c r="C50" t="n">
-        <v>39.87678094783252</v>
+        <v>40.5256658712525</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.7232190521674795</v>
+        <v>-0.07433412874750189</v>
       </c>
       <c r="E50" t="n">
-        <v>0.5230457974180275</v>
+        <v>0.005525562696650188</v>
       </c>
     </row>
     <row r="51">
@@ -1296,13 +1296,13 @@
         <v>40.9</v>
       </c>
       <c r="C51" t="n">
-        <v>40.15228882471894</v>
+        <v>40.86033174156339</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.7477111752810615</v>
+        <v>-0.03966825843661326</v>
       </c>
       <c r="E51" t="n">
-        <v>0.5590720016401862</v>
+        <v>0.001573570727393939</v>
       </c>
     </row>
     <row r="52">
@@ -1313,11 +1313,11 @@
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>3.570425863113588</v>
+        <v>0.959122392995134</v>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="n">
-        <v>13.97177902834835</v>
+        <v>5.465621484408994</v>
       </c>
     </row>
     <row r="53">
@@ -1330,7 +1330,7 @@
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="n">
-        <v>0.279435580566967</v>
+        <v>0.1093124296881799</v>
       </c>
     </row>
   </sheetData>

--- a/partial/sliding_window_results_window_2.xlsx
+++ b/partial/sliding_window_results_window_2.xlsx
@@ -463,13 +463,13 @@
         <v>29.15</v>
       </c>
       <c r="C2" t="n">
-        <v>29.66705863408808</v>
+        <v>28.7985044759573</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5170586340880767</v>
+        <v>-0.3514955240426971</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2673496310850276</v>
+        <v>0.1235491034220503</v>
       </c>
     </row>
     <row r="3">
@@ -480,13 +480,13 @@
         <v>29.35</v>
       </c>
       <c r="C3" t="n">
-        <v>30.15988454009383</v>
+        <v>29.31740043558553</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8098845400938259</v>
+        <v>-0.03259956441446832</v>
       </c>
       <c r="E3" t="n">
-        <v>0.655912968282988</v>
+        <v>0.001062731600013069</v>
       </c>
     </row>
     <row r="4">
@@ -497,13 +497,13 @@
         <v>29.37</v>
       </c>
       <c r="C4" t="n">
-        <v>29.84494678620212</v>
+        <v>29.18334482301621</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4749467862021177</v>
+        <v>-0.1866551769837876</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2255744497237201</v>
+        <v>0.03484015509484908</v>
       </c>
     </row>
     <row r="5">
@@ -514,13 +514,13 @@
         <v>29.54</v>
       </c>
       <c r="C5" t="n">
-        <v>29.24820229833501</v>
+        <v>28.81673666932124</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2917977016649935</v>
+        <v>-0.7232633306787548</v>
       </c>
       <c r="E5" t="n">
-        <v>0.08514589869697256</v>
+        <v>0.5231098455045259</v>
       </c>
     </row>
     <row r="6">
@@ -531,13 +531,13 @@
         <v>29.55</v>
       </c>
       <c r="C6" t="n">
-        <v>29.77028807683576</v>
+        <v>29.56312509652077</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2202880768357574</v>
+        <v>0.01312509652077054</v>
       </c>
       <c r="E6" t="n">
-        <v>0.04852683679599654</v>
+        <v>0.0001722681586795429</v>
       </c>
     </row>
     <row r="7">
@@ -548,13 +548,13 @@
         <v>29.75</v>
       </c>
       <c r="C7" t="n">
-        <v>29.56727933301249</v>
+        <v>29.49360136621713</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1827206669875103</v>
+        <v>-0.2563986337828723</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03338684214436065</v>
+        <v>0.06574025940572346</v>
       </c>
     </row>
     <row r="8">
@@ -565,13 +565,13 @@
         <v>29.84</v>
       </c>
       <c r="C8" t="n">
-        <v>30.08935803597058</v>
+        <v>30.08604601169952</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2493580359705767</v>
+        <v>0.2460460116995158</v>
       </c>
       <c r="E8" t="n">
-        <v>0.06217943010310343</v>
+        <v>0.06053863987323826</v>
       </c>
     </row>
     <row r="9">
@@ -582,13 +582,13 @@
         <v>29.81</v>
       </c>
       <c r="C9" t="n">
-        <v>29.98617848557869</v>
+        <v>29.95476745704475</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1761784855786885</v>
+        <v>0.1447674570447539</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03103885878080017</v>
+        <v>0.02095761661920467</v>
       </c>
     </row>
     <row r="10">
@@ -599,13 +599,13 @@
         <v>29.92</v>
       </c>
       <c r="C10" t="n">
-        <v>29.73711101533921</v>
+        <v>29.90635543839921</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1828889846607886</v>
+        <v>-0.01364456160079186</v>
       </c>
       <c r="E10" t="n">
-        <v>0.03344838071025417</v>
+        <v>0.0001861740612778037</v>
       </c>
     </row>
     <row r="11">
@@ -616,13 +616,13 @@
         <v>29.98</v>
       </c>
       <c r="C11" t="n">
-        <v>29.69799928907306</v>
+        <v>29.60128375279021</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.2820007109269405</v>
+        <v>-0.3787162472097876</v>
       </c>
       <c r="E11" t="n">
-        <v>0.07952440096329984</v>
+        <v>0.1434259959006649</v>
       </c>
     </row>
     <row r="12">
@@ -633,13 +633,13 @@
         <v>30.04</v>
       </c>
       <c r="C12" t="n">
-        <v>29.72613621387445</v>
+        <v>29.85311993656375</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.3138637861255518</v>
+        <v>-0.1868800634362451</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0985104762410661</v>
+        <v>0.03492415810993499</v>
       </c>
     </row>
     <row r="13">
@@ -650,13 +650,13 @@
         <v>30.21</v>
       </c>
       <c r="C13" t="n">
-        <v>29.84922737223416</v>
+        <v>29.73807797401953</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.3607726277658401</v>
+        <v>-0.4719220259804722</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1301568889450694</v>
+        <v>0.2227103986055134</v>
       </c>
     </row>
     <row r="14">
@@ -667,13 +667,13 @@
         <v>30.22</v>
       </c>
       <c r="C14" t="n">
-        <v>29.87118448474057</v>
+        <v>29.99114379320629</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.3488155152594246</v>
+        <v>-0.2288562067937079</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1216722636856978</v>
+        <v>0.05237516338800439</v>
       </c>
     </row>
     <row r="15">
@@ -684,13 +684,13 @@
         <v>30.38</v>
       </c>
       <c r="C15" t="n">
-        <v>29.98279341359101</v>
+        <v>30.04624727596173</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.3972065864089913</v>
+        <v>-0.3337527240382734</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1577730722866835</v>
+        <v>0.1113908808029679</v>
       </c>
     </row>
     <row r="16">
@@ -701,13 +701,13 @@
         <v>30.44</v>
       </c>
       <c r="C16" t="n">
-        <v>30.26108524161952</v>
+        <v>30.5129765737388</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1789147583804827</v>
+        <v>0.07297657373880284</v>
       </c>
       <c r="E16" t="n">
-        <v>0.03201049076634649</v>
+        <v>0.005325580314654929</v>
       </c>
     </row>
     <row r="17">
@@ -718,13 +718,13 @@
         <v>30.48</v>
       </c>
       <c r="C17" t="n">
-        <v>30.15278547970684</v>
+        <v>30.34122287831097</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3272145202931647</v>
+        <v>-0.138777121689035</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1070693422906859</v>
+        <v>0.01925908950429323</v>
       </c>
     </row>
     <row r="18">
@@ -735,13 +735,13 @@
         <v>30.69</v>
       </c>
       <c r="C18" t="n">
-        <v>30.19514282129561</v>
+        <v>30.41571570915758</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4948571787043896</v>
+        <v>-0.2742842908424201</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2448836273152682</v>
+        <v>0.0752318722029293</v>
       </c>
     </row>
     <row r="19">
@@ -752,13 +752,13 @@
         <v>30.75</v>
       </c>
       <c r="C19" t="n">
-        <v>30.60131952062666</v>
+        <v>30.4753606205144</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1486804793733363</v>
+        <v>-0.2746393794855955</v>
       </c>
       <c r="E19" t="n">
-        <v>0.02210588494668508</v>
+        <v>0.07542678876423292</v>
       </c>
     </row>
     <row r="20">
@@ -769,13 +769,13 @@
         <v>30.94</v>
       </c>
       <c r="C20" t="n">
-        <v>30.67738320357709</v>
+        <v>30.5635136522277</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2626167964229076</v>
+        <v>-0.3764863477723033</v>
       </c>
       <c r="E20" t="n">
-        <v>0.06896758176343089</v>
+        <v>0.1417419700589277</v>
       </c>
     </row>
     <row r="21">
@@ -786,13 +786,13 @@
         <v>30.95</v>
       </c>
       <c r="C21" t="n">
-        <v>30.85919113487759</v>
+        <v>30.69365385368444</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.09080886512240482</v>
+        <v>-0.2563461463155612</v>
       </c>
       <c r="E21" t="n">
-        <v>0.008246249984819112</v>
+        <v>0.0657133467308391</v>
       </c>
     </row>
     <row r="22">
@@ -803,13 +803,13 @@
         <v>31.02</v>
       </c>
       <c r="C22" t="n">
-        <v>31.09757034944756</v>
+        <v>31.07621593972941</v>
       </c>
       <c r="D22" t="n">
-        <v>0.07757034944756214</v>
+        <v>0.05621593972940886</v>
       </c>
       <c r="E22" t="n">
-        <v>0.006017159113416904</v>
+        <v>0.003160231879660529</v>
       </c>
     </row>
     <row r="23">
@@ -820,13 +820,13 @@
         <v>31.12</v>
       </c>
       <c r="C23" t="n">
-        <v>31.27601048597176</v>
+        <v>31.32955808800804</v>
       </c>
       <c r="D23" t="n">
-        <v>0.156010485971759</v>
+        <v>0.2095580880080412</v>
       </c>
       <c r="E23" t="n">
-        <v>0.02433927173314442</v>
+        <v>0.04391459224958594</v>
       </c>
     </row>
     <row r="24">
@@ -837,13 +837,13 @@
         <v>31.28</v>
       </c>
       <c r="C24" t="n">
-        <v>31.18419340973565</v>
+        <v>31.33798817979259</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.09580659026435612</v>
+        <v>0.05798817979258786</v>
       </c>
       <c r="E24" t="n">
-        <v>0.009178902738082216</v>
+        <v>0.003362628995657495</v>
       </c>
     </row>
     <row r="25">
@@ -854,13 +854,13 @@
         <v>31.38</v>
       </c>
       <c r="C25" t="n">
-        <v>31.20860949197808</v>
+        <v>31.35677515348965</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.1713905080219149</v>
+        <v>-0.02322484651034884</v>
       </c>
       <c r="E25" t="n">
-        <v>0.02937470624001008</v>
+        <v>0.0005393934954292627</v>
       </c>
     </row>
     <row r="26">
@@ -871,13 +871,13 @@
         <v>31.58</v>
       </c>
       <c r="C26" t="n">
-        <v>31.41963735202371</v>
+        <v>31.67027099680123</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.1603626479762887</v>
+        <v>0.0902709968012303</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0257161788659671</v>
+        <v>0.008148852863487731</v>
       </c>
     </row>
     <row r="27">
@@ -888,13 +888,13 @@
         <v>31.65</v>
       </c>
       <c r="C27" t="n">
-        <v>31.95921673663635</v>
+        <v>31.52521285912132</v>
       </c>
       <c r="D27" t="n">
-        <v>0.3092167366363476</v>
+        <v>-0.1247871408786807</v>
       </c>
       <c r="E27" t="n">
-        <v>0.09561499021603237</v>
+        <v>0.0155718305286757</v>
       </c>
     </row>
     <row r="28">
@@ -905,13 +905,13 @@
         <v>31.88</v>
       </c>
       <c r="C28" t="n">
-        <v>32.68495774151191</v>
+        <v>32.08868933360732</v>
       </c>
       <c r="D28" t="n">
-        <v>0.8049577415119096</v>
+        <v>0.208689333607321</v>
       </c>
       <c r="E28" t="n">
-        <v>0.6479569656199542</v>
+        <v>0.04355123796146772</v>
       </c>
     </row>
     <row r="29">
@@ -922,13 +922,13 @@
         <v>32.28</v>
       </c>
       <c r="C29" t="n">
-        <v>32.92749544001664</v>
+        <v>32.05446298418541</v>
       </c>
       <c r="D29" t="n">
-        <v>0.6474954400166339</v>
+        <v>-0.2255370158145951</v>
       </c>
       <c r="E29" t="n">
-        <v>0.4192503448423344</v>
+        <v>0.05086694550255291</v>
       </c>
     </row>
     <row r="30">
@@ -939,13 +939,13 @@
         <v>32.45</v>
       </c>
       <c r="C30" t="n">
-        <v>33.06663339335906</v>
+        <v>32.27864286774545</v>
       </c>
       <c r="D30" t="n">
-        <v>0.6166333933590522</v>
+        <v>-0.1713571322545562</v>
       </c>
       <c r="E30" t="n">
-        <v>0.3802367418054996</v>
+        <v>0.02936326677450546</v>
       </c>
     </row>
     <row r="31">
@@ -956,13 +956,13 @@
         <v>32.85</v>
       </c>
       <c r="C31" t="n">
-        <v>33.23640948043696</v>
+        <v>32.87946101235892</v>
       </c>
       <c r="D31" t="n">
-        <v>0.38640948043696</v>
+        <v>0.02946101235892229</v>
       </c>
       <c r="E31" t="n">
-        <v>0.1493122865715614</v>
+        <v>0.0008679512492125719</v>
       </c>
     </row>
     <row r="32">
@@ -973,13 +973,13 @@
         <v>32.9</v>
       </c>
       <c r="C32" t="n">
-        <v>33.29977708230282</v>
+        <v>33.0163386529252</v>
       </c>
       <c r="D32" t="n">
-        <v>0.3997770823028262</v>
+        <v>0.1163386529252008</v>
       </c>
       <c r="E32" t="n">
-        <v>0.1598217155345606</v>
+        <v>0.01353468216445034</v>
       </c>
     </row>
     <row r="33">
@@ -990,13 +990,13 @@
         <v>33.1</v>
       </c>
       <c r="C33" t="n">
-        <v>33.33975343964335</v>
+        <v>32.83863660988135</v>
       </c>
       <c r="D33" t="n">
-        <v>0.2397534396433443</v>
+        <v>-0.2613633901186532</v>
       </c>
       <c r="E33" t="n">
-        <v>0.05748171182081473</v>
+        <v>0.06831082169431529</v>
       </c>
     </row>
     <row r="34">
@@ -1007,13 +1007,13 @@
         <v>33.4</v>
       </c>
       <c r="C34" t="n">
-        <v>33.71583827279082</v>
+        <v>33.62695660221546</v>
       </c>
       <c r="D34" t="n">
-        <v>0.3158382727908204</v>
+        <v>0.2269566022154592</v>
       </c>
       <c r="E34" t="n">
-        <v>0.0997538145594887</v>
+        <v>0.05150929928918618</v>
       </c>
     </row>
     <row r="35">
@@ -1024,13 +1024,13 @@
         <v>33.7</v>
       </c>
       <c r="C35" t="n">
-        <v>33.74213643898327</v>
+        <v>33.40944946090692</v>
       </c>
       <c r="D35" t="n">
-        <v>0.04213643898326325</v>
+        <v>-0.2905505390930827</v>
       </c>
       <c r="E35" t="n">
-        <v>0.001775479490190267</v>
+        <v>0.08441961576728098</v>
       </c>
     </row>
     <row r="36">
@@ -1041,13 +1041,13 @@
         <v>34.1</v>
       </c>
       <c r="C36" t="n">
-        <v>33.83770196888512</v>
+        <v>33.63488357270253</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.2622980311148808</v>
+        <v>-0.4651164272974668</v>
       </c>
       <c r="E36" t="n">
-        <v>0.06880025712674298</v>
+        <v>0.2163332909419597</v>
       </c>
     </row>
     <row r="37">
@@ -1058,13 +1058,13 @@
         <v>34.4</v>
       </c>
       <c r="C37" t="n">
-        <v>34.26175461750775</v>
+        <v>34.02686604074501</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.1382453824922436</v>
+        <v>-0.3731339592549858</v>
       </c>
       <c r="E37" t="n">
-        <v>0.01911178578042674</v>
+        <v>0.1392289515493014</v>
       </c>
     </row>
     <row r="38">
@@ -1075,13 +1075,13 @@
         <v>34.9</v>
       </c>
       <c r="C38" t="n">
-        <v>34.53506441515873</v>
+        <v>34.67158873595097</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.3649355848412696</v>
+        <v>-0.2284112640490292</v>
       </c>
       <c r="E38" t="n">
-        <v>0.1331779810834395</v>
+        <v>0.05217170554447535</v>
       </c>
     </row>
     <row r="39">
@@ -1092,13 +1092,13 @@
         <v>35.3</v>
       </c>
       <c r="C39" t="n">
-        <v>35.41163110728882</v>
+        <v>35.47920067161883</v>
       </c>
       <c r="D39" t="n">
-        <v>0.1116311072888223</v>
+        <v>0.1792006716188297</v>
       </c>
       <c r="E39" t="n">
-        <v>0.01246150411452856</v>
+        <v>0.03211288070863963</v>
       </c>
     </row>
     <row r="40">
@@ -1109,13 +1109,13 @@
         <v>35.7</v>
       </c>
       <c r="C40" t="n">
-        <v>35.68715858908152</v>
+        <v>35.75364529843932</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.01284141091848312</v>
+        <v>0.05364529843932075</v>
       </c>
       <c r="E40" t="n">
-        <v>0.0001649018343773375</v>
+        <v>0.00287781804464379</v>
       </c>
     </row>
     <row r="41">
@@ -1126,13 +1126,13 @@
         <v>36.3</v>
       </c>
       <c r="C41" t="n">
-        <v>36.03467250596535</v>
+        <v>36.22837937920274</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.2653274940346506</v>
+        <v>-0.07162062079725473</v>
       </c>
       <c r="E41" t="n">
-        <v>0.07039867909070756</v>
+        <v>0.005129513323384157</v>
       </c>
     </row>
     <row r="42">
@@ -1143,13 +1143,13 @@
         <v>36.8</v>
       </c>
       <c r="C42" t="n">
-        <v>36.6380964444557</v>
+        <v>36.76507789127287</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.1619035555442991</v>
+        <v>-0.03492210872713031</v>
       </c>
       <c r="E42" t="n">
-        <v>0.02621276129788596</v>
+        <v>0.001219553677949511</v>
       </c>
     </row>
     <row r="43">
@@ -1160,13 +1160,13 @@
         <v>37.3</v>
       </c>
       <c r="C43" t="n">
-        <v>36.75375374323595</v>
+        <v>36.91124765795256</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.54624625676405</v>
+        <v>-0.3887523420474395</v>
       </c>
       <c r="E43" t="n">
-        <v>0.2983849730287365</v>
+        <v>0.1511283834473694</v>
       </c>
     </row>
     <row r="44">
@@ -1177,13 +1177,13 @@
         <v>37.9</v>
       </c>
       <c r="C44" t="n">
-        <v>37.77578137501172</v>
+        <v>37.39678901353814</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.1242186249882806</v>
+        <v>-0.503210986461859</v>
       </c>
       <c r="E44" t="n">
-        <v>0.0154302667939791</v>
+        <v>0.2532212968959173</v>
       </c>
     </row>
     <row r="45">
@@ -1194,13 +1194,13 @@
         <v>38.5</v>
       </c>
       <c r="C45" t="n">
-        <v>38.49756896558319</v>
+        <v>38.26882942146615</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.002431034416808586</v>
+        <v>-0.2311705785338489</v>
       </c>
       <c r="E45" t="n">
-        <v>5.909928335707863e-06</v>
+        <v>0.05343983637967441</v>
       </c>
     </row>
     <row r="46">
@@ -1211,13 +1211,13 @@
         <v>38.9</v>
       </c>
       <c r="C46" t="n">
-        <v>39.1968811618345</v>
+        <v>38.85874011835132</v>
       </c>
       <c r="D46" t="n">
-        <v>0.2968811618344986</v>
+        <v>-0.04125988164867778</v>
       </c>
       <c r="E46" t="n">
-        <v>0.08813842425220177</v>
+        <v>0.001702377833662897</v>
       </c>
     </row>
     <row r="47">
@@ -1228,13 +1228,13 @@
         <v>39.4</v>
       </c>
       <c r="C47" t="n">
-        <v>39.67226180578425</v>
+        <v>39.33161024848935</v>
       </c>
       <c r="D47" t="n">
-        <v>0.2722618057842467</v>
+        <v>-0.06838975151064375</v>
       </c>
       <c r="E47" t="n">
-        <v>0.07412649088889889</v>
+        <v>0.004677158111687599</v>
       </c>
     </row>
     <row r="48">
@@ -1245,13 +1245,13 @@
         <v>39.9</v>
       </c>
       <c r="C48" t="n">
-        <v>39.84535288553736</v>
+        <v>39.87640789738438</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.05464711446263948</v>
+        <v>-0.02359210261562339</v>
       </c>
       <c r="E48" t="n">
-        <v>0.002986307119092821</v>
+        <v>0.000556587305826104</v>
       </c>
     </row>
     <row r="49">
@@ -1262,13 +1262,13 @@
         <v>40.1</v>
       </c>
       <c r="C49" t="n">
-        <v>40.27265069933905</v>
+        <v>39.99592231788854</v>
       </c>
       <c r="D49" t="n">
-        <v>0.1726506993390515</v>
+        <v>-0.1040776821114591</v>
       </c>
       <c r="E49" t="n">
-        <v>0.02980826398226357</v>
+        <v>0.01083216391369393</v>
       </c>
     </row>
     <row r="50">
@@ -1279,13 +1279,13 @@
         <v>40.6</v>
       </c>
       <c r="C50" t="n">
-        <v>40.5256658712525</v>
+        <v>40.22588669304565</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.07433412874750189</v>
+        <v>-0.3741133069543494</v>
       </c>
       <c r="E50" t="n">
-        <v>0.005525562696650188</v>
+        <v>0.1399607664403193</v>
       </c>
     </row>
     <row r="51">
@@ -1296,13 +1296,13 @@
         <v>40.9</v>
       </c>
       <c r="C51" t="n">
-        <v>40.86033174156339</v>
+        <v>40.56084829957834</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.03966825843661326</v>
+        <v>-0.3391517004216595</v>
       </c>
       <c r="E51" t="n">
-        <v>0.001573570727393939</v>
+        <v>0.1150238758989031</v>
       </c>
     </row>
     <row r="52">
@@ -1313,11 +1313,11 @@
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>0.959122392995134</v>
+        <v>-7.123220207667952</v>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="n">
-        <v>5.465621484408994</v>
+        <v>3.3744195485554</v>
       </c>
     </row>
     <row r="53">
@@ -1330,7 +1330,7 @@
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="n">
-        <v>0.1093124296881799</v>
+        <v>0.06748839097110799</v>
       </c>
     </row>
   </sheetData>
